--- a/mis7375/homework2/mis7375-homework2-data-dictionary.xlsx
+++ b/mis7375/homework2/mis7375-homework2-data-dictionary.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026</t>
+          <t>10/23/2026</t>
         </is>
       </c>
     </row>
